--- a/artfynd/A 45507-2024 artfynd.xlsx
+++ b/artfynd/A 45507-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61144059</v>
+        <v>77242336</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr Sandbäcken, Vg</t>
+          <t>NO om Ledstugan, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432250.7073508045</v>
+        <v>432145</v>
       </c>
       <c r="R2" t="n">
-        <v>6414931.716637027</v>
+        <v>6414863</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-03-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Något öster om lokalen i sluttningen mot sjön</t>
+          <t>2019-04-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,49 +760,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Pontus Axén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Pontus Axén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Knärotsinventering  i Jönköpings län 2019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77242337</v>
+        <v>83262386</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,14 +811,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO om Ledstugan, Vg</t>
+          <t>Södra Berg, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432251.9167071026</v>
+        <v>432111</v>
       </c>
       <c r="R3" t="n">
-        <v>6414940.207980801</v>
+        <v>6414854</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,29 +843,19 @@
           <t>Bjurbäck</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4EFECB60-437E-43B0-A3DE-1CD6DBFD47BE</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-03-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-04-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>cirka antal skott</t>
+          <t>2008-07-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +870,230 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Marielle Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marielle Gustafsson, Nisse Lennartsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>61144059</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr Sandbäcken, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>432251</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6414932</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bjurbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-08-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-08-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Något öster om lokalen i sluttningen mot sjön</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>77242337</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>NO om Ledstugan, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>432252</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6414940</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mullsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bjurbäck</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-03-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-04-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>cirka antal skott</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Pontus Axén</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Pontus Axén</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Knärotsinventering  i Jönköpings län 2019</t>
         </is>

--- a/artfynd/A 45507-2024 artfynd.xlsx
+++ b/artfynd/A 45507-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Knärotsinventering  i Jönköpings län 2019</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77242336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83262386</t>
         </is>
       </c>
     </row>
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61144059</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,8 +1118,19 @@
           <t>Knärotsinventering  i Jönköpings län 2019</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77242337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>